--- a/Sample_pathway_database_single_file.xlsx
+++ b/Sample_pathway_database_single_file.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="70">
   <si>
     <t>AKT</t>
   </si>
@@ -89,9 +89,6 @@
     <t>ERBB3</t>
   </si>
   <si>
-    <t>PDPK1</t>
-  </si>
-  <si>
     <t>mTORC2</t>
   </si>
   <si>
@@ -113,12 +110,6 @@
     <t>RHEB</t>
   </si>
   <si>
-    <t>IRS1</t>
-  </si>
-  <si>
-    <t>MTOR</t>
-  </si>
-  <si>
     <t>INSR</t>
   </si>
   <si>
@@ -131,18 +122,9 @@
     <t>TSC1/TSC2</t>
   </si>
   <si>
-    <t>IRS2</t>
-  </si>
-  <si>
     <t>AMPK</t>
   </si>
   <si>
-    <t>AKT1S1</t>
-  </si>
-  <si>
-    <t>RPS6</t>
-  </si>
-  <si>
     <t>SMAD7</t>
   </si>
   <si>
@@ -161,9 +143,6 @@
     <t>CABL</t>
   </si>
   <si>
-    <t>WWTR1</t>
-  </si>
-  <si>
     <t>SAV1</t>
   </si>
   <si>
@@ -173,15 +152,9 @@
     <t>NF2</t>
   </si>
   <si>
-    <t>STK3</t>
-  </si>
-  <si>
     <t>TAOK</t>
   </si>
   <si>
-    <t>STK4</t>
-  </si>
-  <si>
     <t>LATS1</t>
   </si>
   <si>
@@ -194,9 +167,6 @@
     <t>TEAD</t>
   </si>
   <si>
-    <t>TP73</t>
-  </si>
-  <si>
     <t>1-phosphatidyl-1D-myo-inositol 3,4,5-trisphosphate</t>
   </si>
   <si>
@@ -231,6 +201,48 @@
   </si>
   <si>
     <t>RAS</t>
+  </si>
+  <si>
+    <t>MST1</t>
+  </si>
+  <si>
+    <t>MST2</t>
+  </si>
+  <si>
+    <t>TAZ</t>
+  </si>
+  <si>
+    <t>YAP1_TEAD</t>
+  </si>
+  <si>
+    <t>IRS1/2(g)</t>
+  </si>
+  <si>
+    <t>SMAD7(g)</t>
+  </si>
+  <si>
+    <t>PDK1</t>
+  </si>
+  <si>
+    <t>S6K1</t>
+  </si>
+  <si>
+    <t>PRAS40</t>
+  </si>
+  <si>
+    <t>S6</t>
+  </si>
+  <si>
+    <t>PTEN(g)</t>
+  </si>
+  <si>
+    <t>DEPTOR</t>
+  </si>
+  <si>
+    <t>ERBB3(g)</t>
+  </si>
+  <si>
+    <t>SPRY2(g)</t>
   </si>
 </sst>
 </file>
@@ -588,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -596,21 +608,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -618,10 +630,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -629,10 +641,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -640,10 +652,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -651,10 +663,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -662,10 +674,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -673,10 +685,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -684,10 +696,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -695,10 +707,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -706,10 +718,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -717,10 +729,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C12">
         <v>-1</v>
@@ -728,10 +740,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C13">
         <v>-1</v>
@@ -739,10 +751,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>-1</v>
@@ -750,10 +762,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -761,10 +773,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>-1</v>
@@ -772,10 +784,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C17">
         <v>-1</v>
@@ -783,10 +795,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>-1</v>
@@ -794,10 +806,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -805,10 +817,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -816,10 +828,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -827,10 +839,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
         <v>48</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -838,47 +850,54 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26"/>
-      <c r="B26"/>
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -888,10 +907,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -901,10 +920,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -914,23 +933,23 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -940,49 +959,49 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -992,10 +1011,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C36">
         <v>-1</v>
@@ -1005,23 +1024,23 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C38">
         <v>-1</v>
@@ -1031,36 +1050,36 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1070,23 +1089,23 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1096,10 +1115,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1109,10 +1128,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1122,10 +1141,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1135,10 +1154,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1148,10 +1167,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1161,10 +1180,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1174,10 +1193,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1187,10 +1206,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -1200,88 +1219,88 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -1291,10 +1310,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="C59">
         <v>-1</v>
@@ -1304,10 +1323,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -1317,10 +1336,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -1330,10 +1349,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -1343,7 +1362,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>64</v>
@@ -1356,13 +1375,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -1382,10 +1401,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C66">
         <v>-1</v>
@@ -1395,10 +1414,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C67">
         <v>-1</v>
@@ -1407,15 +1426,22 @@
       <c r="E67" s="2"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68"/>
-      <c r="B68"/>
+      <c r="A68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B68" t="s">
+        <v>66</v>
+      </c>
+      <c r="C68">
+        <v>-1</v>
+      </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -1423,54 +1449,54 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B71" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B73" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -1478,10 +1504,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -1489,10 +1515,10 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -1500,21 +1526,21 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B77" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C77">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B78" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -1522,10 +1548,10 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C79">
         <v>-1</v>
@@ -1533,21 +1559,21 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C80">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C81">
         <v>-1</v>
@@ -1555,69 +1581,76 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C83">
         <v>-1</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84"/>
-      <c r="B84"/>
+      <c r="A84" t="s">
+        <v>17</v>
+      </c>
+      <c r="B84" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -1625,10 +1658,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -1636,10 +1669,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -1647,10 +1680,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -1658,10 +1691,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B92" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -1669,10 +1702,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B93" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -1680,87 +1713,87 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C94">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C95">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C96">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C97">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C98">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C99">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C100">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -1768,21 +1801,21 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B102" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="C102">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -1790,10 +1823,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="B104" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -1801,10 +1834,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B105" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -1812,32 +1845,32 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C106">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B107" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -1845,10 +1878,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B109" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C109">
         <v>-1</v>
@@ -1856,23 +1889,89 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C110">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B111" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C113">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C117">
         <v>-1</v>
       </c>
     </row>
